--- a/output/2026-09-19_16_Croazia_Osječko-baranjska_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-19_16_Croazia_Osječko-baranjska_Depolverazione_Trattamento_aria.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Distributore B2B utensili/attrezzature industriali con linea usisavači industrijski (aspiratori industriali). Verificato via WebSearch (sito ufficiale + directory mojkvart.hr, radno-vrijeme.com) per EGRESS_BLOCKED su WebFetch diretto. Non specializzato in dust collection ma vende aspiratori industriali a clientela B2B.</t>
+          <t>Distributore B2B utensili/attrezzature industriali con linea usisavači industrijski (aspiratori industriali). Verificato via WebSearch (sito ufficiale + directory mojkvart.hr, radno-vrijeme.com) per EGRESS_BLOCKED su WebFetch diretto. Non specializzato in dust collection ma vende aspiratori industriali a clientela B2B. [DUPLICATO — vedi anche: 2026-09-16_18_Croazia_Osječko-baranjska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Centro Kärcher autorizzato, vendita/assistenza B2B di aspiratori industriali per solidi/liquidi (soluzioni di aspirazione/otprašivanje). Verificato via WebSearch (kaercher.com + catalogo sito proprio) per EGRESS_BLOCKED su WebFetch diretto.</t>
+          <t>Centro Kärcher autorizzato, vendita/assistenza B2B di aspiratori industriali per solidi/liquidi (soluzioni di aspirazione/otprašivanje). Verificato via WebSearch (kaercher.com + catalogo sito proprio) per EGRESS_BLOCKED su WebFetch diretto. [DUPLICATO — vedi anche: 2026-09-16_18_Croazia_Osječko-baranjska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
